--- a/data/trans_orig/IP74A6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A6_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>45065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73586</t>
+          <t>73092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>83571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
